--- a/veriler/AeroModel.xlsx
+++ b/veriler/AeroModel.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Kitap_Calismasi\F16_SIM_MATLAB\veriler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\GIT\F16_Sim_Matlab\veriler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{686A4663-2196-4489-8EFD-3220EFEB07EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F00464-8ACC-4D3F-B952-7241F235B9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E8389A93-520E-4020-85BC-945332E2DC63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8389A93-520E-4020-85BC-945332E2DC63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -164,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -187,6 +186,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,7 +607,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$4</c15:sqref>
@@ -648,7 +648,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -684,7 +684,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$4:$P$4</c15:sqref>
@@ -719,7 +719,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -732,7 +732,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$7</c15:sqref>
@@ -773,7 +773,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -809,7 +809,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$7:$P$7</c15:sqref>
@@ -844,7 +844,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -857,7 +857,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$8</c15:sqref>
@@ -898,7 +898,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -934,7 +934,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$8:$P$8</c15:sqref>
@@ -969,7 +969,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000005-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -982,7 +982,7 @@
                 <c:order val="6"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$9</c15:sqref>
@@ -1029,7 +1029,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -1065,7 +1065,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$9:$P$9</c15:sqref>
@@ -1100,7 +1100,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000006-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -1113,7 +1113,7 @@
                 <c:order val="7"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$10</c15:sqref>
@@ -1160,7 +1160,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -1196,7 +1196,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$10:$P$10</c15:sqref>
@@ -1231,7 +1231,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000007-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -1244,7 +1244,7 @@
                 <c:order val="8"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$11</c15:sqref>
@@ -1291,7 +1291,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -1327,7 +1327,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$11:$P$11</c15:sqref>
@@ -1362,7 +1362,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000008-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -1375,7 +1375,7 @@
                 <c:order val="9"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$12</c15:sqref>
@@ -1422,7 +1422,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -1458,7 +1458,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$12:$P$12</c15:sqref>
@@ -1493,7 +1493,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000009-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -1506,7 +1506,7 @@
                 <c:order val="10"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$13</c15:sqref>
@@ -1553,7 +1553,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -1589,7 +1589,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$13:$P$13</c15:sqref>
@@ -1624,7 +1624,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000A-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -1637,7 +1637,7 @@
                 <c:order val="11"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$I$14</c15:sqref>
@@ -1684,7 +1684,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$2:$P$2</c15:sqref>
@@ -1720,7 +1720,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Sheet1!$J$14:$P$14</c15:sqref>
@@ -1755,7 +1755,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000B-47DB-477B-835E-69C42B8840C5}"/>
                   </c:ext>
@@ -2886,7 +2886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8B84F4-8C95-409E-90D8-D1851A3DEBDC}">
-  <dimension ref="A1:AE84"/>
+  <dimension ref="A1:AI84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -4526,7 +4526,7 @@
       <c r="U32" s="5"/>
       <c r="V32" s="5"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>5</v>
       </c>
@@ -4567,7 +4567,7 @@
       <c r="U33" s="5"/>
       <c r="V33" s="5"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -4618,7 +4618,7 @@
       <c r="U34" s="5"/>
       <c r="V34" s="5"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>-10</v>
       </c>
@@ -4669,7 +4669,7 @@
       <c r="U35" s="5"/>
       <c r="V35" s="5"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>-5</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>-3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>0</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>5</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>10</v>
       </c>
@@ -4849,7 +4849,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>15</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>20</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>25</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>30</v>
       </c>
@@ -5014,7 +5014,7 @@
       <c r="O43" s="9"/>
       <c r="P43" s="9"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>35</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>40</v>
       </c>
@@ -5101,8 +5101,50 @@
       <c r="P45" s="2">
         <v>1.4999999999999999E-2</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U45">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="V45">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="W45">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="X45">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="Y45">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Z45">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AA45">
+        <v>2.3E-2</v>
+      </c>
+      <c r="AC45">
+        <v>1E-3</v>
+      </c>
+      <c r="AD45">
+        <v>2E-3</v>
+      </c>
+      <c r="AE45">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="AF45">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+      <c r="AG45">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="AH45">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="AI45">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5145,8 +5187,50 @@
       <c r="P46" s="2">
         <v>1.4E-2</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U46">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="V46">
+        <v>1.6E-2</v>
+      </c>
+      <c r="W46">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="X46">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Y46">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Z46">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AA46">
+        <v>0.01</v>
+      </c>
+      <c r="AC46">
+        <v>-2.7E-2</v>
+      </c>
+      <c r="AD46">
+        <v>-1.4E-2</v>
+      </c>
+      <c r="AE46">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="AF46">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+      <c r="AG46">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="AH46">
+        <v>-0.01</v>
+      </c>
+      <c r="AI46">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I47">
         <v>0</v>
       </c>
@@ -5171,8 +5255,50 @@
       <c r="P47" s="2">
         <v>1.2999999999999999E-2</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U47">
+        <v>1.4E-2</v>
+      </c>
+      <c r="V47">
+        <v>1.4E-2</v>
+      </c>
+      <c r="W47">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="X47">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Y47">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="Z47">
+        <v>0.01</v>
+      </c>
+      <c r="AA47">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AC47" s="10">
+        <v>-1.7000000000000001E-2</v>
+      </c>
+      <c r="AD47">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="AE47">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="AF47">
+        <v>-0.01</v>
+      </c>
+      <c r="AG47">
+        <v>-1.4E-2</v>
+      </c>
+      <c r="AH47">
+        <v>-4.0000000000000001E-3</v>
+      </c>
+      <c r="AI47">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>11</v>
       </c>
@@ -5205,8 +5331,50 @@
       <c r="P48" s="2">
         <v>1.2999999999999999E-2</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U48">
+        <v>0.01</v>
+      </c>
+      <c r="V48">
+        <v>1.4E-2</v>
+      </c>
+      <c r="W48">
+        <v>1.2E-2</v>
+      </c>
+      <c r="X48">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Y48">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="Z48">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AA48">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AC48" s="10">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="AD48">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="AE48">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="AF48">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="AG48">
+        <v>-1.2E-2</v>
+      </c>
+      <c r="AH48">
+        <v>-2E-3</v>
+      </c>
+      <c r="AI48">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -5234,8 +5402,50 @@
       <c r="P49" s="2">
         <v>1.2E-2</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U49">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="V49">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="W49">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="X49">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Y49">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Z49">
+        <v>0.01</v>
+      </c>
+      <c r="AA49">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AC49" s="10">
+        <v>-1.2E-2</v>
+      </c>
+      <c r="AD49">
+        <v>-1.4E-2</v>
+      </c>
+      <c r="AE49">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="AF49">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="AG49">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+      <c r="AH49">
+        <v>-1E-3</v>
+      </c>
+      <c r="AI49">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I50">
         <v>15</v>
       </c>
@@ -5260,8 +5470,50 @@
       <c r="P50" s="2">
         <v>1.0999999999999999E-2</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U50">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="V50">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="W50">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="X50">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Y50">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="Z50">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AA50">
+        <v>0.01</v>
+      </c>
+      <c r="AC50">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="AD50">
+        <v>-1.9E-2</v>
+      </c>
+      <c r="AE50">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="AF50">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="AG50">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="AH50">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AI50">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I51">
         <v>20</v>
       </c>
@@ -5286,8 +5538,50 @@
       <c r="P51" s="2">
         <v>1.0999999999999999E-2</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U51">
+        <v>1.9E-2</v>
+      </c>
+      <c r="V51">
+        <v>1.2E-2</v>
+      </c>
+      <c r="W51">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="X51">
+        <v>1.4E-2</v>
+      </c>
+      <c r="Y51">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="Z51">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AA51">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AC51">
+        <v>1E-3</v>
+      </c>
+      <c r="AD51">
+        <v>-2.1000000000000001E-2</v>
+      </c>
+      <c r="AE51">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>-2E-3</v>
+      </c>
+      <c r="AH51">
+        <v>1.4E-2</v>
+      </c>
+      <c r="AI51">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I52">
         <v>25</v>
       </c>
@@ -5312,8 +5606,50 @@
       <c r="P52" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U52">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="V52">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="W52">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X52">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Y52">
+        <v>0.01</v>
+      </c>
+      <c r="Z52">
+        <v>0.01</v>
+      </c>
+      <c r="AA52">
+        <v>0.01</v>
+      </c>
+      <c r="AC52">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AD52">
+        <v>2E-3</v>
+      </c>
+      <c r="AE52">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AF52">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AG52">
+        <v>2E-3</v>
+      </c>
+      <c r="AH52">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AI52">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I53">
         <v>30</v>
       </c>
@@ -5338,8 +5674,50 @@
       <c r="P53" s="2">
         <v>6.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>-2E-3</v>
+      </c>
+      <c r="X53">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="Y53">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Z53">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AA53">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AC53">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AD53">
+        <v>1.2E-2</v>
+      </c>
+      <c r="AE53">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AF53">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AG53">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AH53">
+        <v>-1E-3</v>
+      </c>
+      <c r="AI53">
+        <v>-1E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I54">
         <v>35</v>
       </c>
@@ -5364,8 +5742,50 @@
       <c r="P54" s="2">
         <v>1.4E-2</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U54">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="V54">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W54">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X54">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="Y54">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Z54">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AA54">
+        <v>1.4E-2</v>
+      </c>
+      <c r="AC54">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AD54">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AE54">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="AF54">
+        <v>0.01</v>
+      </c>
+      <c r="AG54">
+        <v>1.2E-2</v>
+      </c>
+      <c r="AH54">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AI54">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I55">
         <v>40</v>
       </c>
@@ -5390,8 +5810,50 @@
       <c r="P55" s="2">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U55">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+      <c r="V55">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="W55">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="X55">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Y55">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0.02</v>
+      </c>
+      <c r="AC55">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AD55">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AE55">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AF55">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AG55">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AH55">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AI55">
+        <v>-2E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I56">
         <v>45</v>
       </c>
@@ -5416,8 +5878,50 @@
       <c r="P56" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="U56">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="V56">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="W56">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="X56">
+        <v>1E-3</v>
+      </c>
+      <c r="Y56">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Z56">
+        <v>1E-3</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>1.6E-2</v>
+      </c>
+      <c r="AD56">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AE56">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AF56">
+        <v>0.01</v>
+      </c>
+      <c r="AG56">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AH56">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="AI56">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="J57" s="9" t="s">
         <v>10</v>
       </c>
@@ -5428,7 +5932,7 @@
       <c r="O57" s="9"/>
       <c r="P57" s="9"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I58" t="s">
         <v>3</v>
       </c>
@@ -5454,7 +5958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I59">
         <v>-10</v>
       </c>
@@ -5480,7 +5984,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I60">
         <v>-5</v>
       </c>
@@ -5506,7 +6010,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I61">
         <v>0</v>
       </c>
@@ -5532,7 +6036,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I62">
         <v>5</v>
       </c>
@@ -5558,7 +6062,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I63">
         <v>10</v>
       </c>
@@ -5584,7 +6088,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="I64">
         <v>15</v>
       </c>
